--- a/studentData.xlsx
+++ b/studentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dxcportal-my.sharepoint.com/personal/rakesh_naik_dxc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{3D9A10E2-1AF5-42FA-A5AD-9935ECC12D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8371F45A-FAD1-477D-81E0-E84C86B5AA0A}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{3D9A10E2-1AF5-42FA-A5AD-9935ECC12D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47AB1A54-A35D-4D73-BC25-BDDD0B5AAA64}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B108EBC4-7955-4BA2-B11F-FAD9EE5ED6C6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
   <si>
     <t>Roll No</t>
   </si>
@@ -86,34 +86,7 @@
     <t>student10</t>
   </si>
   <si>
-    <t>student11</t>
-  </si>
-  <si>
-    <t>student12</t>
-  </si>
-  <si>
-    <t>student13</t>
-  </si>
-  <si>
-    <t>student14</t>
-  </si>
-  <si>
-    <t>student15</t>
-  </si>
-  <si>
-    <t>student16</t>
-  </si>
-  <si>
-    <t>student17</t>
-  </si>
-  <si>
-    <t>student18</t>
-  </si>
-  <si>
-    <t>student19</t>
-  </si>
-  <si>
-    <t>student20</t>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -653,142 +626,142 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C16">
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C21">
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
